--- a/data/trans_dic/POLIPATOLOGIA_2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas</t>
+          <t>Población con dos o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,82; 21,81</t>
+          <t>16,23; 22,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,73; 29,49</t>
+          <t>22,42; 29,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,13; 26,59</t>
+          <t>20,03; 26,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,97; 40,78</t>
+          <t>33,18; 40,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,12; 32,99</t>
+          <t>26,64; 33,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,63; 47,83</t>
+          <t>39,94; 47,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,13; 41,83</t>
+          <t>34,44; 42,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,26; 49,27</t>
+          <t>35,93; 49,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,12; 26,64</t>
+          <t>22,21; 26,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,06; 37,42</t>
+          <t>32,19; 37,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,12; 33,11</t>
+          <t>28,28; 33,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,12; 44,21</t>
+          <t>36,95; 44,19</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,33; 22,85</t>
+          <t>17,41; 22,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,4; 26,94</t>
+          <t>21,24; 26,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,9; 26,02</t>
+          <t>20,8; 25,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,43; 29,78</t>
+          <t>10,38; 29,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,7; 37,07</t>
+          <t>30,59; 37,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,95; 40,91</t>
+          <t>34,53; 41,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,05; 40,38</t>
+          <t>34,16; 40,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,59; 48,08</t>
+          <t>42,29; 47,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,13; 29,06</t>
+          <t>25,01; 28,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,05; 33,3</t>
+          <t>28,99; 33,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,12; 32,5</t>
+          <t>28,13; 32,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,82; 37,49</t>
+          <t>22,06; 37,49</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 22,99</t>
+          <t>16,77; 23,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,45; 24,9</t>
+          <t>18,3; 24,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,06; 25,12</t>
+          <t>19,04; 25,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,9; 36,64</t>
+          <t>29,07; 36,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,35; 41,28</t>
+          <t>33,82; 40,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,68; 37,95</t>
+          <t>30,76; 37,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,94; 34,82</t>
+          <t>28,02; 35,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,09; 76,3</t>
+          <t>41,99; 77,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,3; 31,08</t>
+          <t>26,14; 30,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,73; 30,48</t>
+          <t>25,83; 30,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,51; 29,23</t>
+          <t>24,31; 29,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,61; 65,64</t>
+          <t>37,05; 63,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,02; 22,83</t>
+          <t>17,95; 22,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,94; 28,87</t>
+          <t>22,59; 28,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,49; 29,48</t>
+          <t>23,68; 29,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,04; 37,51</t>
+          <t>31,26; 37,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,09; 35,84</t>
+          <t>30,08; 35,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,99; 42,27</t>
+          <t>36,35; 42,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,95; 40,4</t>
+          <t>34,04; 40,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,82; 60,06</t>
+          <t>46,09; 59,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,99; 29,09</t>
+          <t>25,2; 28,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,46; 34,92</t>
+          <t>30,7; 35,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,97; 34,33</t>
+          <t>30,14; 34,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,81; 50,33</t>
+          <t>40,05; 49,88</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,39; 21,02</t>
+          <t>18,45; 21,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,97; 25,93</t>
+          <t>22,82; 25,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,51; 25,31</t>
+          <t>22,39; 25,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,15; 33,44</t>
+          <t>23,27; 33,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,94; 35,34</t>
+          <t>31,94; 35,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,1; 40,54</t>
+          <t>37,09; 40,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,45; 37,77</t>
+          <t>34,58; 37,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,36; 58,39</t>
+          <t>45,39; 58,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,53; 27,87</t>
+          <t>25,7; 27,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,5; 32,73</t>
+          <t>30,49; 32,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,93; 31,19</t>
+          <t>28,88; 31,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,37; 46,04</t>
+          <t>36,6; 45,61</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas</t>
+          <t>Población con dos o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>109765; 151370</t>
+          <t>112626; 155200</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>159917; 207433</t>
+          <t>157689; 204335</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135816; 179460</t>
+          <t>135170; 179156</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>209521; 259121</t>
+          <t>210836; 259795</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>179831; 227112</t>
+          <t>183400; 229364</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>276258; 333415</t>
+          <t>278426; 330542</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>229656; 281447</t>
+          <t>231736; 283574</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>248495; 357338</t>
+          <t>260598; 358804</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>305847; 368209</t>
+          <t>307049; 369518</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>448997; 524143</t>
+          <t>450793; 524198</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>378902; 446221</t>
+          <t>381164; 445217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>491496; 601619</t>
+          <t>502821; 601383</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>166693; 219808</t>
+          <t>167458; 217965</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>217889; 274237</t>
+          <t>216224; 272104</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>213669; 266041</t>
+          <t>212708; 265106</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148252; 355221</t>
+          <t>123864; 353598</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>297321; 358953</t>
+          <t>296218; 359877</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>360750; 422246</t>
+          <t>356429; 423637</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>355135; 421155</t>
+          <t>356275; 421946</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>408321; 460886</t>
+          <t>405406; 455632</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>485136; 561003</t>
+          <t>482730; 558458</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>595637; 682738</t>
+          <t>594405; 680666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>580748; 671197</t>
+          <t>580983; 667894</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>469475; 806570</t>
+          <t>474673; 806701</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>114197; 155982</t>
+          <t>113758; 156304</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>139757; 188666</t>
+          <t>138651; 187652</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144767; 190833</t>
+          <t>144616; 192993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>203653; 258175</t>
+          <t>204870; 258408</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>228062; 282314</t>
+          <t>231263; 279395</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>238433; 294910</t>
+          <t>239037; 295035</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>219345; 273375</t>
+          <t>219964; 275536</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>392873; 712156</t>
+          <t>391903; 724887</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>358339; 423437</t>
+          <t>356080; 421584</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>394864; 467880</t>
+          <t>396417; 468530</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>378623; 451448</t>
+          <t>375546; 449201</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>615995; 1075206</t>
+          <t>606852; 1039056</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>169814; 215153</t>
+          <t>169171; 215473</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>217455; 273605</t>
+          <t>214080; 270270</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>220222; 276378</t>
+          <t>221972; 275973</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>287732; 347671</t>
+          <t>289758; 345563</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>312498; 372272</t>
+          <t>312419; 373585</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>378618; 444664</t>
+          <t>382406; 445088</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>354407; 421683</t>
+          <t>355258; 421452</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>501693; 657593</t>
+          <t>504685; 650521</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>495109; 576240</t>
+          <t>499081; 571935</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>609047; 698265</t>
+          <t>613905; 701677</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>593841; 680276</t>
+          <t>597099; 685778</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>804879; 1017519</t>
+          <t>809725; 1008461</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>602418; 688582</t>
+          <t>604686; 692536</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>787129; 888717</t>
+          <t>782057; 883353</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>764151; 859191</t>
+          <t>759917; 856995</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>835717; 1156801</t>
+          <t>805141; 1153971</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1079246; 1194125</t>
+          <t>1079368; 1189882</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1320215; 1442583</t>
+          <t>1319650; 1442411</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1220979; 1338743</t>
+          <t>1225763; 1344973</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1683891; 2167780</t>
+          <t>1684866; 2187398</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1699278; 1855089</t>
+          <t>1710286; 1847148</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2130636; 2286226</t>
+          <t>2129607; 2282063</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2007492; 2164548</t>
+          <t>2004080; 2159177</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2608595; 3302182</t>
+          <t>2625165; 3271032</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,23; 22,36</t>
+          <t>16,06; 22,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,42; 29,05</t>
+          <t>22,18; 29,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,03; 26,55</t>
+          <t>19,87; 26,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,18; 40,88</t>
+          <t>32,73; 40,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,64; 33,32</t>
+          <t>26,54; 33,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,94; 47,42</t>
+          <t>39,49; 47,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,44; 42,15</t>
+          <t>34,47; 42,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,93; 49,47</t>
+          <t>44,56; 50,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,21; 26,73</t>
+          <t>22,12; 26,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,19; 37,43</t>
+          <t>32,05; 37,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,28; 33,04</t>
+          <t>28,27; 33,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,95; 44,19</t>
+          <t>40,01; 44,89</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 22,66</t>
+          <t>17,49; 22,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,24; 26,73</t>
+          <t>21,21; 26,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,8; 25,93</t>
+          <t>20,66; 25,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,38; 29,64</t>
+          <t>25,7; 31,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,59; 37,16</t>
+          <t>30,73; 37,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,53; 41,04</t>
+          <t>34,51; 41,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,16; 40,46</t>
+          <t>34,2; 40,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,29; 47,53</t>
+          <t>42,26; 47,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,01; 28,93</t>
+          <t>25,1; 29,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,99; 33,2</t>
+          <t>29,14; 33,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,13; 32,34</t>
+          <t>28,27; 32,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,06; 37,49</t>
+          <t>34,99; 38,83</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,77; 23,04</t>
+          <t>17,0; 23,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 24,77</t>
+          <t>18,43; 24,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,04; 25,41</t>
+          <t>18,98; 25,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,07; 36,67</t>
+          <t>28,93; 36,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,82; 40,86</t>
+          <t>33,51; 40,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,76; 37,96</t>
+          <t>30,9; 38,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,02; 35,1</t>
+          <t>27,83; 34,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41,99; 77,66</t>
+          <t>42,71; 49,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,14; 30,95</t>
+          <t>26,06; 30,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,83; 30,53</t>
+          <t>25,6; 30,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,31; 29,08</t>
+          <t>24,21; 29,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,05; 63,43</t>
+          <t>36,69; 41,54</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,95; 22,87</t>
+          <t>17,78; 22,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,59; 28,52</t>
+          <t>23,0; 28,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,68; 29,43</t>
+          <t>23,85; 29,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,26; 37,28</t>
+          <t>30,15; 36,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,08; 35,97</t>
+          <t>30,34; 36,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,35; 42,31</t>
+          <t>36,02; 42,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,04; 40,38</t>
+          <t>34,32; 40,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,09; 59,41</t>
+          <t>43,93; 49,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,2; 28,87</t>
+          <t>24,97; 28,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,7; 35,09</t>
+          <t>30,69; 35,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,14; 34,61</t>
+          <t>30,11; 34,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,05; 49,88</t>
+          <t>38,39; 42,25</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,45; 21,14</t>
+          <t>18,38; 21,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,82; 25,78</t>
+          <t>22,79; 25,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,39; 25,25</t>
+          <t>22,38; 25,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,27; 33,35</t>
+          <t>30,72; 34,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,94; 35,21</t>
+          <t>31,92; 35,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,09; 40,54</t>
+          <t>37,14; 40,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,58; 37,94</t>
+          <t>34,38; 37,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,39; 58,92</t>
+          <t>44,79; 47,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,7; 27,75</t>
+          <t>25,72; 27,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,49; 32,67</t>
+          <t>30,53; 32,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,88; 31,12</t>
+          <t>28,96; 31,24</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,6; 45,61</t>
+          <t>38,18; 40,53</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>234648</t>
+          <t>252485</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>326377</t>
+          <t>349514</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>561025</t>
+          <t>601999</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>112626; 155200</t>
+          <t>111492; 153596</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>157689; 204335</t>
+          <t>156024; 204796</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135170; 179156</t>
+          <t>134102; 177288</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>210836; 259795</t>
+          <t>226046; 280279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>183400; 229364</t>
+          <t>182718; 230628</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>278426; 330542</t>
+          <t>275236; 330504</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>231736; 283574</t>
+          <t>231903; 283046</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>260598; 358804</t>
+          <t>327168; 371813</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>307049; 369518</t>
+          <t>305746; 367926</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>450793; 524198</t>
+          <t>448910; 522762</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>381164; 445217</t>
+          <t>380911; 446673</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>502821; 601383</t>
+          <t>570169; 639593</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>273078</t>
+          <t>297975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>431313</t>
+          <t>481659</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>704391</t>
+          <t>779634</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>167458; 217965</t>
+          <t>168201; 217479</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>216224; 272104</t>
+          <t>215941; 272449</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>212708; 265106</t>
+          <t>211266; 264249</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>123864; 353598</t>
+          <t>269567; 332000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>296218; 359877</t>
+          <t>297605; 361251</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>356429; 423637</t>
+          <t>356196; 425621</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>356275; 421946</t>
+          <t>356705; 424286</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>405406; 455632</t>
+          <t>452843; 509122</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>482730; 558458</t>
+          <t>484467; 562495</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>594405; 680666</t>
+          <t>597438; 680280</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>580983; 667894</t>
+          <t>583923; 668934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>474673; 806701</t>
+          <t>741896; 823297</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>229839</t>
+          <t>259958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>522547</t>
+          <t>372126</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>752386</t>
+          <t>632084</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>113758; 156304</t>
+          <t>115313; 156448</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>138651; 187652</t>
+          <t>139602; 189005</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144616; 192993</t>
+          <t>144182; 191470</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>204870; 258408</t>
+          <t>232326; 289874</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>231263; 279395</t>
+          <t>229131; 277902</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>239037; 295035</t>
+          <t>240145; 297898</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>219964; 275536</t>
+          <t>218487; 273559</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>391903; 724887</t>
+          <t>346934; 398893</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>356080; 421584</t>
+          <t>354974; 420665</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>396417; 468530</t>
+          <t>392922; 468090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>375546; 449201</t>
+          <t>373932; 448483</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>606852; 1039056</t>
+          <t>592712; 671033</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317114</t>
+          <t>330401</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>551732</t>
+          <t>520843</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>868846</t>
+          <t>851245</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>169171; 215473</t>
+          <t>167569; 214483</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>214080; 270270</t>
+          <t>217999; 273076</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>221972; 275973</t>
+          <t>223637; 277369</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>289758; 345563</t>
+          <t>298528; 359095</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>312419; 373585</t>
+          <t>315069; 374532</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>382406; 445088</t>
+          <t>378875; 443949</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>355258; 421452</t>
+          <t>358238; 426421</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>504685; 650521</t>
+          <t>491633; 552279</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>499081; 571935</t>
+          <t>494703; 570327</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>613905; 701677</t>
+          <t>613773; 702275</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>597099; 685778</t>
+          <t>596584; 681221</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>809725; 1008461</t>
+          <t>809781; 891039</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1054679</t>
+          <t>1140819</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1831969</t>
+          <t>1724142</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2886648</t>
+          <t>2864962</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>604686; 692536</t>
+          <t>602391; 693201</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>782057; 883353</t>
+          <t>780825; 885096</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>759917; 856995</t>
+          <t>759512; 861636</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>805141; 1153971</t>
+          <t>1085220; 1205055</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1079368; 1189882</t>
+          <t>1078673; 1189146</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1319650; 1442411</t>
+          <t>1321643; 1434835</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1225763; 1344973</t>
+          <t>1218532; 1342725</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1684866; 2187398</t>
+          <t>1673647; 1779174</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1710286; 1847148</t>
+          <t>1711947; 1860969</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2129607; 2282063</t>
+          <t>2132730; 2295311</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2004080; 2159177</t>
+          <t>2009158; 2167617</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2625165; 3271032</t>
+          <t>2775215; 2946273</t>
         </is>
       </c>
     </row>
